--- a/pipeline/ptms_coordinated_phosphosites/Supplementary_Table_S6b.xlsx
+++ b/pipeline/ptms_coordinated_phosphosites/Supplementary_Table_S6b.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 6b" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp. Table 6b" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 6b'!$A$1:$W$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supp. Table 6b'!$A$1:$W$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -538,7 +538,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Residue number in entry</t>
+          <t>PDB residue number</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -2800,63 +2800,63 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+          <t>Notes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="43" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Search. Every human X-ray structure in the PDB at ≤ 2.0 Å resolution, released by 16 September 2026, containing phosphoserine, phosphothreonine or phosphotyrosine (1,236 entries). This gave 101 unique phosphosites in 71 proteins with a phosphate coordinated by Lys or Arg, of which the 23 listed are also buried in a chain in which they are fully coordinated.</t>
+          <t>PDB search: Every human X-ray structure in the PDB at ≤ 2.0 Å resolution, released up to and including 16 September 2026, containing phosphoserine, phosphothreonine or phosphotyrosine (1,236 entries). This gave 101 unique phosphosites in 71 proteins with a phosphate coordinated by Lys or Arg, of which the 23 listed are also buried in a chain in which they are fully coordinated (≥ 2 Arg/Lys contacts).</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Coordination. A Lys or Arg side chain of the same chain with a charged-group atom (Lys NZ; Arg NE, CZ, NH1, NH2) within 4.0 Å of a phosphate atom, the ionic-contact criterion of Supplementary Table 4. Fully coordinated: two or more such side chains.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="69" customHeight="1">
+          <t>Coordination: A Lys or Arg side chain of the same chain with a charged-group atom (Lys NZ; Arg NE, CZ, NH1, NH2) within 4.0 Å of a phosphate atom, the ionic-contact criterion of Supplementary Table 4. Fully coordinated: two or more such side chains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Burial. Relative solvent accessibility (RSA) ≤ 0.25, computed with DSSP on the isolated chain, matching the monomeric analysis elsewhere in this work, and normalised to the empirical maxima of Tien et al. (2013). No maxima have been published for phosphorylated residues; for these, the empirical maximum of the parent residue was scaled by the phospho/parent ratio obtained by repeating the Gly-X-Gly enumeration of Tien et al.: SEP 226, TPO 243, PTR 334 Å². 'RSA using the unmodified parent reference' is the lowest RSA recalculated with the smaller maxima of Ser, Thr and Tyr, the more conservative convention. Entries in which a partner chain packs against the site show a lower accessibility for the whole entry than for the isolated chain.</t>
+          <t>Burial: Relative solvent accessibility (RSA) ≤ 0.25, computed with DSSP on the isolated chain, matching the monomeric analysis elsewhere in this work, and normalised to the empirical maxima of Tien et al. (2013). For phosphorylated residues, the empirical maximum of the parent residue was scaled by the phospho/parent ratio obtained by repeating the Gly-X-Gly enumeration of Tien et al.: SEP 226 Å², TPO 243 Å², PTR 334 Å². 'RSA using the unmodified parent reference' is the lowest RSA recalculated with the smaller maxima of unmodified Ser, Thr or Tyr. Entries in which a partner chain packs against the site show a lower accessibility for the whole entry than for the isolated chain, as expected.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="43" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Exclusions. Co-crystallised substrate phosphopeptides (chains under 30 residues), non-human chains, and phosphoresidues that SIFTS does not map to UniProt, such as those in expression tags. Each residue was mapped to UniProt individually through SIFTS and accepted only where the canonical sequence carries the corresponding Ser, Thr or Tyr. Ubiquitin, encoded by four genes with an identical sequence, is counted once.</t>
+          <t>Exclusions: Co-crystallised substrate phosphopeptides (chains under 30 residues), non-human chains, and phosphoresidues that SIFTS does not map to UniProt, such as those in expression tags. Each residue was mapped to UniProt individually through SIFTS and accepted only where the canonical sequence carries the corresponding Ser, Thr or Tyr. Ubiquitin, encoded by four genes with an identical sequence, is counted once.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Numbering. Phosphosites follow UniProt. 'Residue number in entry' and the coordinating residues are numbered as deposited in the representative entry.</t>
+          <t>Numbering: Phosphosites (e.g. pSer65) follow UniProt numbering. The 'PDB residue number' column and the coordinating residues are numbered as deposited in the representative PDB entry.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Representative entry. The entry and chain with the most coordinating side chains, then the lowest RSA, then the best resolution. 'Lowest SASA' and 'Lowest RSA' are the lowest values among the entries in which the site is coordinated by Lys or Arg.</t>
+          <t>Representative entry: The entry and chain with the most coordinating side chains, then the lowest RSA, then the best resolution. 'Lowest SASA' and 'Lowest RSA' are the lowest values among the entries in which the site is coordinated by Lys or Arg.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Reproducibility. Whether the site is buried and fully coordinated in all, at least half, or fewer than half of the entries in which the phosphorylated residue is resolved.</t>
+          <t>Reproducibility: Whether the site is buried and fully coordinated in all, at least half, or fewer than half of the entries in which the phosphorylated residue is resolved.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Protein kinase and structural context. Protein kinases are the proteins with a domain in the Kincore alignment of human protein kinase domains (Modi &amp; Dunbrack, 2019), in which the activation loop runs from the DFG to the APE motif.</t>
+          <t>Kinase structural context: Kinase domains are from the Kincore alignment of human protein kinase domains (Modi &amp; Dunbrack, 2019), in which the activation loop runs from the DFG to the APE motif.</t>
         </is>
       </c>
     </row>

--- a/pipeline/ptms_coordinated_phosphosites/Supplementary_Table_S6b.xlsx
+++ b/pipeline/ptms_coordinated_phosphosites/Supplementary_Table_S6b.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp. Table 6b" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supp. Table 6b'!$A$1:$W$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supp. Table 6b'!$A$1:$Y$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -483,16 +483,18 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="44" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
-    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="44" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="52" customHeight="1">
@@ -563,50 +565,60 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Highest RSA across entries</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>RSA using the unmodified parent reference</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Buried under both reference conventions</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Arg/Lys contacts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Coordinating residues (charged-group distance, Å)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Entries in which the site is resolved</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Entries buried and fully coordinated</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Reproducibility</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PDB entries in which the site is resolved</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>UniProt modification evidence</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Protein kinase</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Structural context</t>
         </is>
@@ -665,49 +677,57 @@
         <v>0.018</v>
       </c>
       <c r="N2" s="4" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="O2" s="4" t="n">
         <v>0.028</v>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Lys211 NZ–O2P (2.53); Arg163 NE–O1P (2.69); Lys161 NZ–O3P (2.77)</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="T2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>at least half of entries</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>6GLC*, 8IKM</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Not a protein kinase</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="17" customHeight="1">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -760,43 +780,51 @@
         <v>0.027</v>
       </c>
       <c r="N3" s="4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O3" s="4" t="n">
         <v>0.035</v>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Arg156 NE–O3P (2.61); Arg176 NH1–O2P (2.79)</t>
         </is>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>1QCF*, 5H09*, 5H0B*, 5H0G*, 5H0H*, 9BYJ*</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>Kinase, outside the kinase domain</t>
         </is>
@@ -855,43 +883,51 @@
         <v>0.031</v>
       </c>
       <c r="N4" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O4" s="4" t="n">
         <v>0.049</v>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Lys273 NZ–O2P (2.76); Arg272 NH2–O3P (2.86)</t>
         </is>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>3TMP*</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Not a protein kinase</t>
         </is>
@@ -950,43 +986,51 @@
         <v>0.062</v>
       </c>
       <c r="N5" s="4" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="O5" s="4" t="n">
         <v>0.092</v>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Arg131 NH1–O1P (2.70); Arg133 NH2–O2P (3.02); Arg121 NE–O2P (3.41)</t>
         </is>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>9KBO*</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>Not annotated in UniProt</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>Not a protein kinase</t>
         </is>
@@ -1045,49 +1089,57 @@
         <v>0.066</v>
       </c>
       <c r="N6" s="4" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="O6" s="4" t="n">
         <v>0.098</v>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Lys127 NZ–O2P (2.55); Arg138 NH1–O1P (2.80)</t>
         </is>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>9KBO*</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>Not annotated in UniProt</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>Not a protein kinase</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="43" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -1140,43 +1192,51 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="N7" s="4" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>0.133</v>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Arg439 NH2–O2P (2.76); Arg472 NH2–O1P (2.80); Arg359 NH2–O3P (2.92)</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>at least half of entries</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>2J0I*, 2Q0N*, 4FIH*, 4FII*, 4JDI*, 5VEF*, 5XVA*, 5ZJW*, 6WLY*, 7S48*, 8AHG*, 4JDH</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>Activation loop, C-terminal segment (up to the APE motif)</t>
         </is>
@@ -1235,43 +1295,51 @@
         <v>0.093</v>
       </c>
       <c r="N8" s="4" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="O8" s="4" t="n">
         <v>0.147</v>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Arg23 NH2–O3P (3.02); Arg293 CZ–O2P (3.28)</t>
         </is>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="T8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>at least half of entries</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>5JN5*, 5VG7*, 5VBI</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>Not a protein kinase</t>
         </is>
@@ -1330,43 +1398,51 @@
         <v>0.12</v>
       </c>
       <c r="N9" s="4" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="O9" s="4" t="n">
         <v>0.157</v>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Arg175 NH2–O2P (2.72); Arg155 NE–O2P (2.77)</t>
         </is>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>1FMK*, 2SRC*, 8JN8*</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>Kinase, outside the kinase domain</t>
         </is>
@@ -1425,49 +1501,57 @@
         <v>0.144</v>
       </c>
       <c r="N10" s="4" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="O10" s="4" t="n">
         <v>0.188</v>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Arg706 NH2–O1P (2.72); Arg682 NH1–O1P (3.34)</t>
         </is>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="S10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>3CD3*</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>Activation loop, N-terminal segment (from the DFG motif)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="69" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1520,43 +1604,51 @@
         <v>0.16</v>
       </c>
       <c r="N11" s="4" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="O11" s="4" t="n">
         <v>0.239</v>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Arg334 NH2–O2P (2.78); Arg347 NH1–O2P (2.80)</t>
         </is>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="S11" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="S11" s="2" t="n">
+      <c r="T11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>fewer than half of entries</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>2NRU*, 2OIB*, 6O8U*, 6O94*, 6THX*, 6UYA*, 8TVN*, 8W3X*, 9R9G*, 9R9K*, 5UIT, 6N8G, 6O95, 8SCE, 8TX0, 8UCB, 8UCC, 8W3W, 9NA2, 9NA5, 9PSS</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>Activation loop, variable insert</t>
         </is>
@@ -1615,43 +1707,51 @@
         <v>0.173</v>
       </c>
       <c r="N12" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O12" s="4" t="n">
         <v>0.258</v>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Arg267 NH2–O3P (2.53); Lys135 NZ–O2P (2.83); Arg217 NH2–O1P (3.01)</t>
         </is>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="S12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="T12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>at least half of entries</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>3WE4*, 3WF8*, 3WF7</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>Activation loop, C-terminal segment (up to the APE motif)</t>
         </is>
@@ -1710,43 +1810,51 @@
         <v>0.18</v>
       </c>
       <c r="N13" s="4" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="O13" s="4" t="n">
         <v>0.235</v>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Arg1649 NE–O3P (2.64); Lys1659 NZ–O2P (3.20)</t>
         </is>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="S13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="T13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>at least half of entries</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>3CLY*, 2PVF</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" s="2" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>Activation loop, N-terminal segment (from the DFG motif)</t>
         </is>
@@ -1805,49 +1913,57 @@
         <v>0.185</v>
       </c>
       <c r="N14" s="4" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="O14" s="4" t="n">
         <v>0.276</v>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Arg70 NH2–O1P (2.61); Arg173 NH2–O2P (2.80); Arg149 NH1–O2P (2.82); Lys66 NZ–O3P (3.20)</t>
         </is>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>6ZQS*</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>Activation loop, C-terminal segment (up to the APE motif)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="82" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1900,49 +2016,57 @@
         <v>0.19</v>
       </c>
       <c r="N15" s="4" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="O15" s="4" t="n">
         <v>0.301</v>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Lys342 NZ–O2P (2.71); Arg336 NH2–O3P (2.76)</t>
         </is>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="S15" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="T15" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>at least half of entries</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>3AMA*, 3L9L*, 3L9M*, 3OOG*, 3OVV*, 3OWP*, 3POO*, 3VQH*, 4UJ1*, 4UJ9*, 4UJA*, 4UJB*, 4WB5*, 4WB7*, 4WB8*, 5BX6*, 5BX7*, 5IZJ*, 6FRX*, 6QJ7*, 3AGM, 3L9N, 3NX8</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>Kinase, outside the kinase domain</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="43" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1995,43 +2119,51 @@
         <v>0.193</v>
       </c>
       <c r="N16" s="4" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="O16" s="4" t="n">
         <v>0.288</v>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Lys367 NZ–O2P (3.46); Lys441 NZ–O1P (3.55)</t>
         </is>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="S16" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="S16" s="2" t="n">
+      <c r="T16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>fewer than half of entries</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>9NA2*, 2OIB, 6N8G, 6O94, 6O95, 6UYA, 8SCE, 8TVN, 8TX0, 8UCB, 8W3W, 8W3X, 9NA5, 9PSS</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>Activation loop, N-terminal segment (from the DFG motif)</t>
         </is>
@@ -2090,43 +2222,51 @@
         <v>0.216</v>
       </c>
       <c r="N17" s="4" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>0.282</v>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>Arg770 NH1–O3P (2.61); Lys907 NZ–O1P (2.75); Arg897 NE–O3P (3.17)</t>
         </is>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="S17" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="T17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>at least half of entries</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>2X2L*, 4CKJ*, 6NE7*, 6NJA*, 6I83</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>Activation loop, N-terminal segment (from the DFG motif)</t>
         </is>
@@ -2185,49 +2325,57 @@
         <v>0.222</v>
       </c>
       <c r="N18" s="4" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="O18" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>Arg385 NH1–O1P (2.73); Arg419 NH2–O2P (2.99)</t>
         </is>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>1YI6*</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>Activation loop, N-terminal segment (from the DFG motif)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="82" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -2280,43 +2428,51 @@
         <v>0.226</v>
       </c>
       <c r="N19" s="4" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O19" s="4" t="n">
         <v>0.337</v>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>Arg180 NH1–O1P (2.61); Arg286 NH2–O2P (2.72); Arg255 NH2–O1P (2.86)</t>
         </is>
       </c>
-      <c r="R19" s="2" t="n">
+      <c r="S19" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="S19" s="2" t="n">
+      <c r="T19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>fewer than half of entries</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>5G1X*, 7ZTL*, 5DNR, 5L8K, 5L8L, 5ORL, 5ORS, 5ORV, 5ORW, 5ORX, 5ORY, 5ORZ, 5OS0, 5OS1, 5OS3, 5OS4, 5OS5, 5OSD, 5OSE, 5OSF, 6R4A, 6VPL, 6VPM, 8C14, 9BZG, 9BZL</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>Activation loop, C-terminal segment (up to the APE motif)</t>
         </is>
@@ -2375,49 +2531,57 @@
         <v>0.226</v>
       </c>
       <c r="N20" s="4" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O20" s="4" t="n">
         <v>0.337</v>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="Q20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Arg224 NH2–O3P (3.46); Lys165 NZ–O3P (3.58)</t>
         </is>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="S20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>all entries</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>3D0E*</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>By similarity or large-scale (ECO:0000250, ECO:0007744, ECO:0000305)</t>
         </is>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>Kinase, outside the kinase domain</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="82" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -2470,49 +2634,57 @@
         <v>0.23</v>
       </c>
       <c r="N21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="4" t="n">
         <v>0.364</v>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Arg129 NH1–O1P (2.56); Arg204 NH2–O1P (2.65); Lys228 NZ–O2P (3.31)</t>
         </is>
       </c>
-      <c r="R21" s="2" t="n">
+      <c r="S21" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="S21" s="2" t="n">
+      <c r="T21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>fewer than half of entries</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>4AW1*, 1H1W, 1UU3, 1UU7, 2XCH, 3HRC, 3HRF, 3NUU, 3ORZ, 3QC4, 3QD3, 3RCJ, 3RWP, 4A06, 4A07, 4AW0, 4CT1, 4CT2, 4RQK, 4RQV, 4RRV, 4XX9, 5ACK, 5LVL, 5LVM, 5LVN, 5LVO, 5MRD, 8DQT</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>Activation loop, C-terminal segment (up to the APE motif)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="69" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -2565,49 +2737,57 @@
         <v>0.235</v>
       </c>
       <c r="N22" s="4" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="O22" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>Arg220 NH1–O2P (2.72); Lys244 NZ–O3P (2.86)</t>
         </is>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="S22" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="T22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>fewer than half of entries</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>4WB7*, 3AGM, 3AMA, 3L9L, 3L9M, 3L9N, 3NX8, 3OOG, 3OVV, 3OWP, 3POO, 3VQH, 4UJ1, 4UJ9, 4UJA, 4UJB, 4WB5, 4WB8, 5BX6, 5BX7, 5IZJ, 6FRX, 6QJ7</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>Activation loop, C-terminal segment (up to the APE motif)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="82" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -2660,43 +2840,51 @@
         <v>0.243</v>
       </c>
       <c r="N23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="4" t="n">
         <v>0.362</v>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Arg126 NH1–O2P (2.79); Arg150 NH2–O1P (2.82); Arg50 NH2–O1P (2.89)</t>
         </is>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="S23" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="S23" s="2" t="n">
+      <c r="T23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>fewer than half of entries</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>3BHT*, 3DDQ*, 4CFV*, 11GV, 1H1R, 1H1S, 1OIU, 2CCH, 2IW9, 3QHW, 3TNW, 4EOI, 4EOJ, 4EOP, 5CYI, 6ATH, 6GUC, 6GUE, 7ACK, 7QHL, 8VQ3, 8VQ4, 9OB3, 9OB4, 9OB6</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>Activation loop, C-terminal segment (up to the APE motif)</t>
         </is>
@@ -2755,43 +2943,51 @@
         <v>0.247</v>
       </c>
       <c r="N24" s="4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="O24" s="4" t="n">
         <v>0.368</v>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>Lys277 NZ–O1P (2.47); Arg253 NH2–O3P (2.64); Lys258 NZ–O3P (2.77); Arg318 NH1–O2P (3.03)</t>
         </is>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="S24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="T24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>fewer than half of entries</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>3A8X*, 5LI1, 5LI9</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>Kinase, outside the kinase domain</t>
         </is>
@@ -2807,73 +3003,200 @@
     <row r="27" ht="43" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>PDB search: Every human X-ray structure in the PDB at ≤ 2.0 Å resolution, released up to and including 16 September 2026, containing phosphoserine, phosphothreonine or phosphotyrosine (1,236 entries). This gave 101 unique phosphosites in 71 proteins with a phosphate coordinated by Lys or Arg, of which the 23 listed are also buried in a chain in which they are fully coordinated (≥ 2 Arg/Lys contacts).</t>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>PDB search:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Every human X-ray structure in the PDB at ≤ 2.0 Å resolution, released up to and including 16 September 2026, containing phosphoserine, phosphothreonine or phosphotyrosine (1,236 entries). This gave 101 unique phosphosites in 71 proteins with a phosphate coordinated by Lys or Arg, of which the 23 listed are also buried in a chain in which they are fully coordinated (≥ 2 Arg/Lys contacts).</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Coordination: A Lys or Arg side chain of the same chain with a charged-group atom (Lys NZ; Arg NE, CZ, NH1, NH2) within 4.0 Å of a phosphate atom, the ionic-contact criterion of Supplementary Table 4. Fully coordinated: two or more such side chains.</t>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Coordination:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> A Lys or Arg side chain of the same chain with a charged-group atom (Lys NZ; Arg NE, CZ, NH1, NH2) within 4.0 Å of a phosphate atom, the ionic-contact criterion of Supplementary Table 4. Fully coordinated: two or more such side chains.</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Burial: Relative solvent accessibility (RSA) ≤ 0.25, computed with DSSP on the isolated chain, matching the monomeric analysis elsewhere in this work, and normalised to the empirical maxima of Tien et al. (2013). For phosphorylated residues, the empirical maximum of the parent residue was scaled by the phospho/parent ratio obtained by repeating the Gly-X-Gly enumeration of Tien et al.: SEP 226 Å², TPO 243 Å², PTR 334 Å². 'RSA using the unmodified parent reference' is the lowest RSA recalculated with the smaller maxima of unmodified Ser, Thr or Tyr. Entries in which a partner chain packs against the site show a lower accessibility for the whole entry than for the isolated chain, as expected.</t>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Burial:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Relative solvent accessibility (RSA) ≤ 0.25, computed with DSSP on the isolated chain, matching the monomeric analysis elsewhere in this work, and normalised to the empirical maxima of Tien et al. (2013). For phosphorylated residues, the empirical maximum of the parent residue was scaled by the phospho/parent ratio obtained by repeating the Gly-X-Gly enumeration of Tien et al.: SEP 226 Å², TPO 243 Å², PTR 334 Å². 'RSA using the unmodified parent reference' is the lowest RSA recalculated with the smaller maxima of unmodified Ser, Thr or Tyr. Entries in which a partner chain packs against the site show a lower accessibility for the whole entry than for the isolated chain, as expected.</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="30" ht="43" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Exclusions: Co-crystallised substrate phosphopeptides (chains under 30 residues), non-human chains, and phosphoresidues that SIFTS does not map to UniProt, such as those in expression tags. Each residue was mapped to UniProt individually through SIFTS and accepted only where the canonical sequence carries the corresponding Ser, Thr or Tyr. Ubiquitin, encoded by four genes with an identical sequence, is counted once.</t>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Exclusions:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Co-crystallised substrate phosphopeptides (chains under 30 residues), non-human chains, and phosphoresidues that SIFTS does not map to UniProt, such as those in expression tags. Each residue was mapped to UniProt individually through SIFTS and accepted only where the canonical sequence carries the corresponding Ser, Thr or Tyr. Ubiquitin, encoded by four genes with an identical sequence, is counted once.</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Numbering: Phosphosites (e.g. pSer65) follow UniProt numbering. The 'PDB residue number' column and the coordinating residues are numbered as deposited in the representative PDB entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Numbering:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Phosphosites (e.g. pSer65) follow UniProt numbering. The 'PDB residue number' column and the coordinating residues are numbered as deposited in the representative PDB entry.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="43" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Representative entry: The entry and chain with the most coordinating side chains, then the lowest RSA, then the best resolution. 'Lowest SASA' and 'Lowest RSA' are the lowest values among the entries in which the site is coordinated by Lys or Arg.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1">
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Representative entry:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> The entry and chain with the most coordinating side chains, then the lowest RSA, then the best resolution. 'Lowest SASA' and 'Lowest RSA' are the lowest values among the entries in which the site is coordinated by Lys or Arg. 'Highest RSA' is the highest value among all entries in which the phosphorylated residue is resolved (RSA values are capped at 1).</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Reproducibility: Whether the site is buried and fully coordinated in all, at least half, or fewer than half of the entries in which the phosphorylated residue is resolved.</t>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Reproducibility:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Whether the site is buried and fully coordinated in all, at least half, or fewer than half of the entries in which the phosphorylated residue is resolved. 'PDB entries in which the site is resolved' lists these entries, with those in which the site is buried and fully coordinated first and marked with an asterisk.</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Kinase structural context: Kinase domains are from the Kincore alignment of human protein kinase domains (Modi &amp; Dunbrack, 2019), in which the activation loop runs from the DFG to the APE motif.</t>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Kinase structural context:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Kinase domains are from the Kincore alignment of human protein kinase domains (Modi &amp; Dunbrack, 2019), in which the activation loop runs from the DFG to the APE motif.</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Code and complete results: https://github.com/langbnj/ptms/tree/main/pipeline/ptms_coordinated_phosphosites</t>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Code and complete results:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> https://github.com/langbnj/ptms/tree/main/pipeline/ptms_coordinated_phosphosites</t>
+          </r>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W24"/>
-  <mergeCells count="9">
+  <autoFilter ref="A1:Y24"/>
+  <mergeCells count="10">
     <mergeCell ref="A27:N27"/>
     <mergeCell ref="A31:N31"/>
     <mergeCell ref="A34:N34"/>
     <mergeCell ref="A35:N35"/>
+    <mergeCell ref="A26:N26"/>
     <mergeCell ref="A30:N30"/>
     <mergeCell ref="A29:N29"/>
     <mergeCell ref="A33:N33"/>

--- a/pipeline/ptms_coordinated_phosphosites/Supplementary_Table_S6b.xlsx
+++ b/pipeline/ptms_coordinated_phosphosites/Supplementary_Table_S6b.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp. Table 6b" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Supp. Table 6b" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supp. Table 6b'!$A$1:$Y$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supp. Table 6b'!$A$1:$Y$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -677,7 +677,7 @@
         <v>0.018</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.469</v>
+        <v>0.465</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>0.028</v>
@@ -780,7 +780,7 @@
         <v>0.027</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>0.035</v>
@@ -977,16 +977,16 @@
         <v>15</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>15</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>0.092</v>
@@ -1080,16 +1080,16 @@
         <v>16</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.066</v>
+        <v>0.068</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>16</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.066</v>
+        <v>0.068</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>0.098</v>
@@ -1183,16 +1183,16 @@
         <v>19</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>19</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>0.133</v>
@@ -1286,16 +1286,16 @@
         <v>21</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>21</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="O8" s="4" t="n">
         <v>0.147</v>
@@ -1389,16 +1389,16 @@
         <v>40</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>40</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>0.157</v>
@@ -1492,16 +1492,16 @@
         <v>48</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>48</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="O10" s="4" t="n">
         <v>0.188</v>
@@ -1595,16 +1595,16 @@
         <v>39</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.16</v>
+        <v>0.165</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>39</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.16</v>
+        <v>0.165</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.354</v>
+        <v>0.364</v>
       </c>
       <c r="O11" s="4" t="n">
         <v>0.239</v>
@@ -1698,16 +1698,16 @@
         <v>56</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.23</v>
+        <v>0.237</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>42</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.173</v>
+        <v>0.178</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.23</v>
+        <v>0.237</v>
       </c>
       <c r="O12" s="4" t="n">
         <v>0.258</v>
@@ -1801,16 +1801,16 @@
         <v>60</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>60</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.254</v>
+        <v>0.259</v>
       </c>
       <c r="O13" s="4" t="n">
         <v>0.235</v>
@@ -1860,33 +1860,33 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="82" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MAPK14</t>
+          <t>PRKACA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Q16539</t>
+          <t>P17612</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Mitogen-activated protein kinase 14</t>
+          <t>cAMP-dependent protein kinase catalytic subunit alpha</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>pThr180</t>
+          <t>pSer339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6ZQS</t>
+          <t>3VQH</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1898,25 +1898,25 @@
         <v>1.95</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>180</v>
+        <v>338</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.185</v>
+        <v>0.189</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.185</v>
+        <v>0.189</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.185</v>
+        <v>0.404</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.276</v>
+        <v>0.301</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
@@ -1924,27 +1924,27 @@
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Arg70 NH2–O1P (2.61); Arg173 NH2–O2P (2.80); Arg149 NH1–O2P (2.82); Lys66 NZ–O3P (3.20)</t>
+          <t>Lys342 NZ–O2P (2.71); Arg336 NH2–O3P (2.76)</t>
         </is>
       </c>
       <c r="S14" s="2" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>all entries</t>
+          <t>at least half of entries</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6ZQS*</t>
+          <t>3AMA*, 3L9L*, 3L9M*, 3OOG*, 3OVV*, 3OWP*, 3POO*, 3VQH*, 4UJ1*, 4UJ9*, 4UJA*, 4UJB*, 4WB5*, 4WB7*, 4WB8*, 5BX6*, 5BX7*, 5IZJ*, 6FRX*, 6QJ7*, 3AGM, 3L9N, 3NX8</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1959,37 +1959,37 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>Activation loop, C-terminal segment (up to the APE motif)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="82" customHeight="1">
+          <t>Kinase, outside the kinase domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PRKACA</t>
+          <t>MAPK14</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>P17612</t>
+          <t>Q16539</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>cAMP-dependent protein kinase catalytic subunit alpha</t>
+          <t>Mitogen-activated protein kinase 14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>pSer339</t>
+          <t>pThr180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3VQH</t>
+          <t>6ZQS</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,25 +2001,25 @@
         <v>1.95</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>338</v>
+        <v>180</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.407</v>
+        <v>0.191</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.301</v>
+        <v>0.276</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -2027,27 +2027,27 @@
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Lys342 NZ–O2P (2.71); Arg336 NH2–O3P (2.76)</t>
+          <t>Arg70 NH2–O1P (2.61); Arg173 NH2–O2P (2.80); Arg149 NH1–O2P (2.82); Lys66 NZ–O3P (3.20)</t>
         </is>
       </c>
       <c r="S15" s="2" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>at least half of entries</t>
+          <t>all entries</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3AMA*, 3L9L*, 3L9M*, 3OOG*, 3OVV*, 3OWP*, 3POO*, 3VQH*, 4UJ1*, 4UJ9*, 4UJA*, 4UJB*, 4WB5*, 4WB7*, 4WB8*, 5BX6*, 5BX7*, 5IZJ*, 6FRX*, 6QJ7*, 3AGM, 3L9N, 3NX8</t>
+          <t>6ZQS*</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>Kinase, outside the kinase domain</t>
+          <t>Activation loop, C-terminal segment (up to the APE motif)</t>
         </is>
       </c>
     </row>
@@ -2110,16 +2110,16 @@
         <v>47</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.193</v>
+        <v>0.199</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>47</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.193</v>
+        <v>0.199</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.872</v>
+        <v>0.898</v>
       </c>
       <c r="O16" s="4" t="n">
         <v>0.288</v>
@@ -2213,16 +2213,16 @@
         <v>72</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.216</v>
+        <v>0.22</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>72</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.216</v>
+        <v>0.22</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.266</v>
+        <v>0.271</v>
       </c>
       <c r="O17" s="4" t="n">
         <v>0.282</v>
@@ -2316,16 +2316,16 @@
         <v>74</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>74</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.704</v>
+        <v>0.716</v>
       </c>
       <c r="O18" s="4" t="n">
         <v>0.29</v>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>AURKA</t>
+          <t>PDPK1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>O14965</t>
+          <t>O15530</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Aurora kinase A</t>
+          <t>3-phosphoinositide-dependent protein kinase 1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>pThr288</t>
+          <t>pSer241</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5G1X</t>
+          <t>4AW1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2410,28 +2410,28 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>288</v>
+        <v>241</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.226</v>
+        <v>0.228</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.226</v>
+        <v>0.228</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.889</v>
+        <v>1</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.337</v>
+        <v>0.364</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2443,14 +2443,14 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Arg180 NH1–O1P (2.61); Arg286 NH2–O2P (2.72); Arg255 NH2–O1P (2.86)</t>
+          <t>Arg204 NH2–O1P (2.65); Arg129 NH1–O1P (2.69); Lys228 NZ–O2P (3.31)</t>
         </is>
       </c>
       <c r="S19" s="2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5G1X*, 7ZTL*, 5DNR, 5L8K, 5L8L, 5ORL, 5ORS, 5ORV, 5ORW, 5ORX, 5ORY, 5ORZ, 5OS0, 5OS1, 5OS3, 5OS4, 5OS5, 5OSD, 5OSE, 5OSF, 6R4A, 6VPL, 6VPM, 8C14, 9BZG, 9BZL</t>
+          <t>4AW1*, 1H1W, 1UU3, 1UU7, 2XCH, 3HRC, 3HRF, 3NUU, 3ORZ, 3QC4, 3QD3, 3RCJ, 3RWP, 4A06, 4A07, 4AW0, 4CT1, 4CT2, 4RQK, 4RQV, 4RRV, 4XX9, 5ACK, 5LVL, 5LVM, 5LVN, 5LVO, 5MRD, 8DQT</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2478,60 +2478,60 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="43" customHeight="1">
+    <row r="20" ht="82" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AKT2</t>
+          <t>AURKA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>P31751</t>
+          <t>O14965</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>RAC-beta serine/threonine-protein kinase</t>
+          <t>Aurora kinase A</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>pThr451</t>
+          <t>pThr288</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3D0E</t>
+          <t>5G1X</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>451</v>
+        <v>288</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>55</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>55</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.288</v>
+        <v>0.915</v>
       </c>
       <c r="O20" s="4" t="n">
         <v>0.337</v>
@@ -2542,32 +2542,32 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Arg180 NH1–O1P (2.61); Arg286 NH2–O2P (2.72); Arg255 NH2–O1P (2.86)</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="T20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>Arg224 NH2–O3P (3.46); Lys165 NZ–O3P (3.58)</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>all entries</t>
+          <t>fewer than half of entries</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3D0E*</t>
+          <t>5G1X*, 7ZTL*, 5DNR, 5L8K, 5L8L, 5ORL, 5ORS, 5ORV, 5ORW, 5ORX, 5ORY, 5ORZ, 5OS0, 5OS1, 5OS3, 5OS4, 5OS5, 5OSD, 5OSE, 5OSF, 6R4A, 6VPL, 6VPM, 8C14, 9BZG, 9BZL</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>By similarity or large-scale (ECO:0000250, ECO:0007744, ECO:0000305)</t>
+          <t>Experimental (ECO:0000269)</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -2577,100 +2577,100 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>Kinase, outside the kinase domain</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="82" customHeight="1">
+          <t>Activation loop, C-terminal segment (up to the APE motif)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="43" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>PDPK1</t>
+          <t>AKT2</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>O15530</t>
+          <t>P31751</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3-phosphoinositide-dependent protein kinase 1</t>
+          <t>RAC-beta serine/threonine-protein kinase</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>pSer241</t>
+          <t>pThr451</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4AW1</t>
+          <t>3D0E</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>241</v>
+        <v>451</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.23</v>
+        <v>0.233</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.23</v>
+        <v>0.233</v>
       </c>
       <c r="N21" s="4" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Arg224 NH2–O3P (3.46); Lys165 NZ–O3P (3.58)</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>Arg129 NH1–O1P (2.56); Arg204 NH2–O1P (2.65); Lys228 NZ–O2P (3.31)</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="n">
-        <v>29</v>
       </c>
       <c r="T21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>fewer than half of entries</t>
+          <t>all entries</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4AW1*, 1H1W, 1UU3, 1UU7, 2XCH, 3HRC, 3HRF, 3NUU, 3ORZ, 3QC4, 3QD3, 3RCJ, 3RWP, 4A06, 4A07, 4AW0, 4CT1, 4CT2, 4RQK, 4RQV, 4RRV, 4XX9, 5ACK, 5LVL, 5LVM, 5LVN, 5LVO, 5MRD, 8DQT</t>
+          <t>3D0E*</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>Experimental (ECO:0000269)</t>
+          <t>By similarity or large-scale (ECO:0000250, ECO:0007744, ECO:0000305)</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>Activation loop, C-terminal segment (up to the APE motif)</t>
+          <t>Kinase, outside the kinase domain</t>
         </is>
       </c>
     </row>
@@ -2728,16 +2728,16 @@
         <v>57</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.235</v>
+        <v>0.242</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>57</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.235</v>
+        <v>0.242</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.449</v>
+        <v>0.462</v>
       </c>
       <c r="O22" s="4" t="n">
         <v>0.35</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="82" customHeight="1">
+    <row r="23" ht="69" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -2831,13 +2831,13 @@
         <v>59</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.243</v>
+        <v>0.25</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>59</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.243</v>
+        <v>0.25</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>25</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3BHT*, 3DDQ*, 4CFV*, 11GV, 1H1R, 1H1S, 1OIU, 2CCH, 2IW9, 3QHW, 3TNW, 4EOI, 4EOJ, 4EOP, 5CYI, 6ATH, 6GUC, 6GUE, 7ACK, 7QHL, 8VQ3, 8VQ4, 9OB3, 9OB4, 9OB6</t>
+          <t>3DDQ*, 11GV, 1H1R, 1H1S, 1OIU, 2CCH, 2IW9, 3BHT, 3QHW, 3TNW, 4CFV, 4EOI, 4EOJ, 4EOP, 5CYI, 6ATH, 6GUC, 6GUE, 7ACK, 7QHL, 8VQ3, 8VQ4, 9OB3, 9OB4, 9OB6</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -2890,118 +2890,15 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>PRKCI</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>P41743</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Protein kinase C iota type</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>pThr564</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3A8X</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>555</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="O24" s="4" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>Lys277 NZ–O1P (2.47); Arg253 NH2–O3P (2.64); Lys258 NZ–O3P (2.77); Arg318 NH1–O2P (3.03)</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>fewer than half of entries</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>3A8X*, 5LI1, 5LI9</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>Experimental (ECO:0000269)</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t>Kinase, outside the kinase domain</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="43" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="26" ht="43" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3016,13 +2913,13 @@
               <rFont val="Helvetica Neue"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve"> Every human X-ray structure in the PDB at ≤ 2.0 Å resolution, released up to and including 16 September 2026, containing phosphoserine, phosphothreonine or phosphotyrosine (1,236 entries). This gave 101 unique phosphosites in 71 proteins with a phosphate coordinated by Lys or Arg, of which the 23 listed are also buried in a chain in which they are fully coordinated (≥ 2 Arg/Lys contacts).</t>
+            <t xml:space="preserve"> Every human X-ray structure in the PDB at ≤ 2.0 Å resolution, released up to and including 16 September 2026, containing phosphoserine, phosphothreonine or phosphotyrosine (1,236 entries). This gave 102 unique phosphosites in 72 proteins with a phosphate coordinated by Lys or Arg, of which the 22 listed are also buried in a chain in which they are fully coordinated (≥ 2 Arg/Lys contacts).</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3042,8 +2939,8 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3058,13 +2955,13 @@
               <rFont val="Helvetica Neue"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve"> Relative solvent accessibility (RSA) ≤ 0.25, computed with DSSP on the isolated chain, matching the monomeric analysis elsewhere in this work, and normalised to the empirical maxima of Tien et al. (2013). For phosphorylated residues, the empirical maximum of the parent residue was scaled by the phospho/parent ratio obtained by repeating the Gly-X-Gly enumeration of Tien et al.: SEP 226 Å², TPO 243 Å², PTR 334 Å². 'RSA using the unmodified parent reference' is the lowest RSA recalculated with the smaller maxima of unmodified Ser, Thr or Tyr. Entries in which a partner chain packs against the site show a lower accessibility for the whole entry than for the isolated chain, as expected.</t>
+            <t xml:space="preserve"> Relative solvent accessibility (RSA) ≤ 0.25, computed with DSSP on the isolated chain, matching the monomeric analysis elsewhere in this work, and normalised to the empirical maxima of Tien et al. (2013). For phosphorylated residues, the empirical maximum of the parent residue was scaled by the phospho/parent ratio obtained by repeating the Gly-X-Gly enumeration of Tien et al.: SEP 228 Å², TPO 236 Å², PTR 328 Å². 'RSA using the unmodified parent reference' is the lowest RSA recalculated with the smaller maxima of unmodified Ser, Thr or Tyr. Entries in which a partner chain packs against the site show a lower accessibility for the whole entry than for the isolated chain, as expected.</t>
           </r>
         </is>
       </c>
     </row>
-    <row r="30" ht="43" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="29" ht="43" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3084,8 +2981,8 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3105,8 +3002,8 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="43" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="31" ht="43" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3126,8 +3023,8 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3147,8 +3044,8 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3168,8 +3065,8 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3190,15 +3087,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y24"/>
+  <autoFilter ref="A1:Y23"/>
   <mergeCells count="10">
     <mergeCell ref="A27:N27"/>
     <mergeCell ref="A31:N31"/>
     <mergeCell ref="A34:N34"/>
-    <mergeCell ref="A35:N35"/>
     <mergeCell ref="A26:N26"/>
     <mergeCell ref="A30:N30"/>
     <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A25:N25"/>
     <mergeCell ref="A33:N33"/>
     <mergeCell ref="A28:N28"/>
     <mergeCell ref="A32:N32"/>

--- a/pipeline/ptms_coordinated_phosphosites/Supplementary_Table_S6b.xlsx
+++ b/pipeline/ptms_coordinated_phosphosites/Supplementary_Table_S6b.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3044,8 +3044,29 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="56" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Alternative positions:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Helvetica Neue"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Where part of a residue is modelled in alternative positions (alternate locations), position A was used. This applies to the phosphoresidue or a coordinating Lys or Arg of three sites in some of their entries: PGM1 pSer117 (5VBI, 5VG7), PDPK1 pSer241 (Arg129 in 4AW0, 4AW1, 4RQK, 4RRV, 4XX9 and 5LVO) and PRKACA pThr198 (Lys189 in 4WB5). All three sites are buried and fully coordinated in at least one entry whichever position is used. Only the coordination by Arg23 of PGM1 depends on the position, in 5VG7 (position A only) and 5VBI (position B only).</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3065,8 +3086,8 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3088,10 +3109,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Y23"/>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A27:N27"/>
     <mergeCell ref="A31:N31"/>
     <mergeCell ref="A34:N34"/>
+    <mergeCell ref="A35:N35"/>
     <mergeCell ref="A26:N26"/>
     <mergeCell ref="A30:N30"/>
     <mergeCell ref="A29:N29"/>
